--- a/artfynd/A 72989-2021 artfynd.xlsx
+++ b/artfynd/A 72989-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72989-2021 artfynd.xlsx
+++ b/artfynd/A 72989-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,124 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>66001793</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nyckelbyön, Övre Ulleruds K:a, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>412657</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6617151</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-05-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-05-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Dan Mangsbo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Dan Mangsbo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 72989-2021 artfynd.xlsx
+++ b/artfynd/A 72989-2021 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>66001793</v>
       </c>
       <c r="B4" t="n">
-        <v>56947</v>
+        <v>56948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72989-2021 artfynd.xlsx
+++ b/artfynd/A 72989-2021 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>66001793</v>
       </c>
       <c r="B4" t="n">
-        <v>56948</v>
+        <v>56952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72989-2021 artfynd.xlsx
+++ b/artfynd/A 72989-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64846248</v>
+        <v>81935677</v>
       </c>
       <c r="B2" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Alcedo atthis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,19 +712,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nyckelbyön, Övre Ulleruds K:a, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412657.2329045981</v>
+        <v>412657</v>
       </c>
       <c r="R2" t="n">
-        <v>6617151.444923244</v>
+        <v>6617151</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-03-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-03-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-03-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,37 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81935677</v>
+        <v>66001793</v>
       </c>
       <c r="B3" t="n">
-        <v>56387</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100004</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alcedo atthis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,20 +821,19 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nyckelbyön, Övre Ulleruds K:a, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412657.2329045981</v>
+        <v>412657</v>
       </c>
       <c r="R3" t="n">
-        <v>6617151.444923244</v>
+        <v>6617151</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -880,22 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-03-31</t>
+          <t>2017-05-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-03-31</t>
+          <t>2017-05-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,32 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66001793</v>
+        <v>64846248</v>
       </c>
       <c r="B4" t="n">
-        <v>56952</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -998,22 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-05-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2016-03-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-05-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2016-03-25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 72989-2021 artfynd.xlsx
+++ b/artfynd/A 72989-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81935677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66001793</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,8 +1022,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64846248</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>